--- a/artfynd/A 18375-2021 artfynd.xlsx
+++ b/artfynd/A 18375-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18375-2021 artfynd.xlsx
+++ b/artfynd/A 18375-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2195,10 +2195,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>77310737</v>
+        <v>77310733</v>
       </c>
       <c r="B14" t="n">
-        <v>95511</v>
+        <v>101680</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221944</v>
+        <v>222412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>77310733</v>
+        <v>77310736</v>
       </c>
       <c r="B15" t="n">
-        <v>101680</v>
+        <v>93044</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222412</v>
+        <v>2809</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2429,10 +2429,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>77310736</v>
+        <v>85491705</v>
       </c>
       <c r="B16" t="n">
-        <v>93044</v>
+        <v>100515</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2441,25 +2441,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2809</v>
+        <v>223246</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2469,17 +2469,17 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bromsberget, Dlr</t>
+          <t>Bromsberget NR, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>538979.9747819613</v>
+        <v>539301.0708582069</v>
       </c>
       <c r="R16" t="n">
-        <v>6648795.122465831</v>
+        <v>6648686.881508341</v>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2019-04-23</t>
+          <t>2020-05-16</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2513,12 +2513,17 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2019-04-23</t>
+          <t>2020-05-16</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>30 cm diam i granplantering</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2531,25 +2536,35 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Lågörtädellövskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>f d ädellövskog, nu granplantering med inslag av ädellöv och hassel</t>
+        </is>
+      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Urban Gunnarsson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Urban Gunnarsson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>85491705</v>
+        <v>85499653</v>
       </c>
       <c r="B17" t="n">
-        <v>100515</v>
+        <v>98520</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2558,25 +2573,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>223246</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2590,13 +2605,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>539301.0708582069</v>
+        <v>538855.209133552</v>
       </c>
       <c r="R17" t="n">
-        <v>6648686.881508341</v>
+        <v>6648976.034500331</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2636,11 +2651,6 @@
       <c r="AB17" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>30 cm diam i granplantering</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2660,7 +2670,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>f d ädellövskog, nu granplantering med inslag av ädellöv och hassel</t>
+          <t>f d ädellövskog, nu granplantering med inslag av ädellövträd och hassel. Några ytor har granen avverkats.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2678,10 +2688,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>85499653</v>
+        <v>85497339</v>
       </c>
       <c r="B18" t="n">
-        <v>98520</v>
+        <v>100515</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2690,25 +2700,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>223246</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2722,10 +2732,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538855.209133552</v>
+        <v>539296.1212253831</v>
       </c>
       <c r="R18" t="n">
-        <v>6648976.034500331</v>
+        <v>6648727.881977995</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2768,6 +2778,11 @@
       <c r="AB18" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2 st almar á 50 cm diameter. Båda spår efter ringbarkning på 1970-talet.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2805,10 +2820,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>85497339</v>
+        <v>85498721</v>
       </c>
       <c r="B19" t="n">
-        <v>100515</v>
+        <v>98520</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2817,25 +2832,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223246</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2849,10 +2864,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>539296.1212253831</v>
+        <v>539200.1668484705</v>
       </c>
       <c r="R19" t="n">
-        <v>6648727.881977995</v>
+        <v>6648743.884325723</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2895,11 +2910,6 @@
       <c r="AB19" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2 st almar á 50 cm diameter. Båda spår efter ringbarkning på 1970-talet.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2937,10 +2947,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>85498721</v>
+        <v>85499504</v>
       </c>
       <c r="B20" t="n">
-        <v>98520</v>
+        <v>79512</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2949,31 +2959,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>229558</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2981,10 +2990,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>539200.1668484705</v>
+        <v>538828.7492366196</v>
       </c>
       <c r="R20" t="n">
-        <v>6648743.884325723</v>
+        <v>6648917.184397662</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3064,10 +3073,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>85499504</v>
+        <v>85499260</v>
       </c>
       <c r="B21" t="n">
-        <v>79512</v>
+        <v>100515</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3076,30 +3085,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229558</v>
+        <v>223246</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3107,10 +3117,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538828.7492366196</v>
+        <v>538918.1677774671</v>
       </c>
       <c r="R21" t="n">
-        <v>6648917.184397662</v>
+        <v>6648806.986588518</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3153,6 +3163,11 @@
       <c r="AB21" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2x30 cm diam</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3190,7 +3205,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>85499260</v>
+        <v>85499602</v>
       </c>
       <c r="B22" t="n">
         <v>100515</v>
@@ -3234,10 +3249,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>538918.1677774671</v>
+        <v>538855.209133552</v>
       </c>
       <c r="R22" t="n">
-        <v>6648806.986588518</v>
+        <v>6648976.034500331</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3284,7 +3299,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2x30 cm diam</t>
+          <t>2 träd á 50 cm diam</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3322,10 +3337,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>85499602</v>
+        <v>85499204</v>
       </c>
       <c r="B23" t="n">
-        <v>100515</v>
+        <v>104490</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3334,29 +3349,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>223246</v>
+        <v>219686</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3366,10 +3389,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>538855.209133552</v>
+        <v>538973.7992418759</v>
       </c>
       <c r="R23" t="n">
-        <v>6648976.034500331</v>
+        <v>6648810.076319813</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3414,11 +3437,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>2 träd á 50 cm diam</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3437,6 +3455,26 @@
       <c r="AI23" t="inlineStr">
         <is>
           <t>f d ädellövskog, nu granplantering med inslag av ädellövträd och hassel. Några ytor har granen avverkats.</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>mycket stor och grov grupp</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Corylus avellana # mycket stor och grov grupp</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3454,10 +3492,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>85499204</v>
+        <v>85498705</v>
       </c>
       <c r="B24" t="n">
-        <v>104490</v>
+        <v>101680</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3470,16 +3508,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219686</v>
+        <v>222412</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3487,16 +3525,8 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3506,10 +3536,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>538973.7992418759</v>
+        <v>539200.1668484705</v>
       </c>
       <c r="R24" t="n">
-        <v>6648810.076319813</v>
+        <v>6648743.884325723</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3572,26 +3602,6 @@
       <c r="AI24" t="inlineStr">
         <is>
           <t>f d ädellövskog, nu granplantering med inslag av ädellövträd och hassel. Några ytor har granen avverkats.</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>hassel</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>mycket stor och grov grupp</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Corylus avellana # mycket stor och grov grupp</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3609,10 +3619,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>85498705</v>
+        <v>85499319</v>
       </c>
       <c r="B25" t="n">
-        <v>101680</v>
+        <v>98520</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3625,21 +3635,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3653,10 +3663,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>539200.1668484705</v>
+        <v>538880.846489468</v>
       </c>
       <c r="R25" t="n">
-        <v>6648743.884325723</v>
+        <v>6648827.11945152</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3699,6 +3709,11 @@
       <c r="AB25" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3736,10 +3751,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>85499319</v>
+        <v>85499333</v>
       </c>
       <c r="B26" t="n">
-        <v>98520</v>
+        <v>104490</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3752,25 +3767,33 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>219686</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3780,10 +3803,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538880.846489468</v>
+        <v>538850.1821589966</v>
       </c>
       <c r="R26" t="n">
-        <v>6648827.11945152</v>
+        <v>6648881.865721084</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3826,11 +3849,6 @@
       <c r="AB26" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3868,10 +3886,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>85499333</v>
+        <v>85499454</v>
       </c>
       <c r="B27" t="n">
-        <v>104490</v>
+        <v>101680</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3884,16 +3902,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219686</v>
+        <v>222412</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3901,16 +3919,8 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3920,10 +3930,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>538850.1821589966</v>
+        <v>538835.8320960096</v>
       </c>
       <c r="R27" t="n">
-        <v>6648881.865721084</v>
+        <v>6648911.251441649</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3966,6 +3976,11 @@
       <c r="AB27" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>område utan gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4003,10 +4018,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>85499454</v>
+        <v>85499234</v>
       </c>
       <c r="B28" t="n">
-        <v>101680</v>
+        <v>104490</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4019,16 +4034,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222412</v>
+        <v>219686</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4036,8 +4051,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
@@ -4047,10 +4070,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>538835.8320960096</v>
+        <v>538962.2137358818</v>
       </c>
       <c r="R28" t="n">
-        <v>6648911.251441649</v>
+        <v>6648814.960421516</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4095,11 +4118,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>område utan gran</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4118,6 +4136,21 @@
       <c r="AI28" t="inlineStr">
         <is>
           <t>f d ädellövskog, nu granplantering med inslag av ädellövträd och hassel. Några ytor har granen avverkats.</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4135,10 +4168,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>85499234</v>
+        <v>85499612</v>
       </c>
       <c r="B29" t="n">
-        <v>104490</v>
+        <v>99398</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4151,33 +4184,25 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219686</v>
+        <v>221235</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -4187,10 +4212,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>538962.2137358818</v>
+        <v>538855.209133552</v>
       </c>
       <c r="R29" t="n">
-        <v>6648814.960421516</v>
+        <v>6648976.034500331</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4253,21 +4278,6 @@
       <c r="AI29" t="inlineStr">
         <is>
           <t>f d ädellövskog, nu granplantering med inslag av ädellövträd och hassel. Några ytor har granen avverkats.</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>hassel</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4285,10 +4295,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>85499612</v>
+        <v>85499278</v>
       </c>
       <c r="B30" t="n">
-        <v>99398</v>
+        <v>100515</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4297,25 +4307,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221235</v>
+        <v>223246</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4329,10 +4339,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>538855.209133552</v>
+        <v>538906.154732269</v>
       </c>
       <c r="R30" t="n">
-        <v>6648976.034500331</v>
+        <v>6648804.857502504</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4375,6 +4385,11 @@
       <c r="AB30" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>25 cm diam</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4412,7 +4427,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>85499278</v>
+        <v>85497236</v>
       </c>
       <c r="B31" t="n">
         <v>100515</v>
@@ -4456,10 +4471,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>538906.154732269</v>
+        <v>539294.7766815184</v>
       </c>
       <c r="R31" t="n">
-        <v>6648804.857502504</v>
+        <v>6648712.848290487</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4506,7 +4521,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>25 cm diam</t>
+          <t>45 cm diameter. spår av misslyckad ringbarkning på 1970-talet.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4544,7 +4559,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>85497236</v>
+        <v>85499069</v>
       </c>
       <c r="B32" t="n">
         <v>100515</v>
@@ -4588,10 +4603,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>539294.7766815184</v>
+        <v>538980.0804336292</v>
       </c>
       <c r="R32" t="n">
-        <v>6648712.848290487</v>
+        <v>6648785.110867479</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4638,7 +4653,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>45 cm diameter. spår av misslyckad ringbarkning på 1970-talet.</t>
+          <t>40 cm diam</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4676,10 +4691,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>85499069</v>
+        <v>95311536</v>
       </c>
       <c r="B33" t="n">
-        <v>100515</v>
+        <v>81963</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4688,45 +4703,50 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>223246</v>
+        <v>204936</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Praktscharlakansskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Sarcoscypha coccinea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(Jacq.:Fr.) Lambotte</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bromsberget NR, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>538980.0804336292</v>
+        <v>539247.9768504123</v>
       </c>
       <c r="R33" t="n">
-        <v>6648785.110867479</v>
+        <v>6648680.809838843</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4750,7 +4770,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2020-05-16</t>
+          <t>2018-04-23</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4760,7 +4780,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2020-05-16</t>
+          <t>2018-04-23</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4768,164 +4788,27 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>40 cm diam</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Lågörtädellövskog</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>f d ädellövskog, nu granplantering med inslag av ädellövträd och hassel. Några ytor har granen avverkats.</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Nina Söderström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Nina Söderström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>95311536</v>
-      </c>
-      <c r="B34" t="n">
-        <v>81963</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>204936</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Praktscharlakansskål</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Sarcoscypha coccinea</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Bromsberget NR, Dlr</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>539247.9768504123</v>
-      </c>
-      <c r="R34" t="n">
-        <v>6648680.809838843</v>
-      </c>
-      <c r="S34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Söderbärke</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2018-04-23</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2018-04-23</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Nina Söderström</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Nina Söderström</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
